--- a/jogos_2024-10-07.xlsx
+++ b/jogos_2024-10-07.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FeralpiSalò</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.8</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['45+7', '50', '61', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.38</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45572.64583333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>FeralpiSalò</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
       <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.44</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.19</v>
-      </c>
       <c r="X8" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AD8" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['45+7', '50', '61', '90+2']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45572.64583333334</v>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['39', '75', '85']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45572.66666666666</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45572.66666666666</v>
@@ -1794,32 +1794,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
       <c r="M11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA11" t="n">
         <v>4.2</v>
       </c>
-      <c r="N11" t="n">
-        <v>6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.58</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['39', '75', '85']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45572.66666666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['53', '54']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['30', '43']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['40', '53', '80', '84']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45572.83333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['53', '54']</t>
+          <t>['40', '53', '80', '84']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['30', '43']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45572.83333333334</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
         <v>1.57</v>
@@ -2766,50 +2766,50 @@
         <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['60', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['10', '14', '62']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45572.875</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.57</v>
@@ -2895,50 +2895,50 @@
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Y19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['10', '14', '62']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['60', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45572.875</v>
